--- a/code/resultados/NWJSSP_OADG_NEH(SwapMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapMixedImprovement).xlsx
@@ -1,45 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clase\Desktop\OADG\Heuristica-Trabajo-2\code\resultados\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89A1F3E-342E-4570-85C6-27F12B3EF027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ft06" sheetId="1" r:id="rId1"/>
-    <sheet name="ft06r" sheetId="2" r:id="rId2"/>
-    <sheet name="ft10" sheetId="3" r:id="rId3"/>
-    <sheet name="ft10r" sheetId="4" r:id="rId4"/>
-    <sheet name="ft20" sheetId="5" r:id="rId5"/>
-    <sheet name="ft20r" sheetId="6" r:id="rId6"/>
-    <sheet name="tai_j10_m10_1" sheetId="7" r:id="rId7"/>
-    <sheet name="tai_j10_m10_1r" sheetId="8" r:id="rId8"/>
+    <sheet name="ft06" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ft06r" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ft10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -360,36 +414,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>362</v>
-      </c>
-      <c r="B1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="n">
+        <v>356</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>48</v>
-      </c>
-      <c r="C2">
+      <c r="B2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>56</v>
-      </c>
-      <c r="E2">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>32</v>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -398,35 +456,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>388</v>
       </c>
-      <c r="B1">
+      <c r="B1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>39</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>47</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>17</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>76</v>
       </c>
     </row>
@@ -436,47 +498,51 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>12110</v>
       </c>
-      <c r="B1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>46</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>132</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>955</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1543</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1319</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>909</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>377</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1133</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>587</v>
       </c>
     </row>
@@ -486,47 +552,51 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>12629</v>
       </c>
-      <c r="B1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>529</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1441</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>46</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1070</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>743</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1639</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>907</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>768</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>377</v>
       </c>
     </row>
@@ -536,77 +606,81 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>21767</v>
       </c>
-      <c r="B1">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>281</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>496</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>676</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>767</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1603</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>630</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>149</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1666</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1104</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>1762</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>180</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1444</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>1250</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>919</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>399</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>62</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1887</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>1035</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>348</v>
       </c>
     </row>
@@ -616,77 +690,81 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>21479</v>
       </c>
-      <c r="B1">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1380</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1137</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1228</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1951</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1812</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>433</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1491</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>170</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>660</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>531</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1643</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>316</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>1070</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>783</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>703</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>880</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>101</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>74</v>
       </c>
     </row>
@@ -696,48 +774,52 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>120779</v>
-      </c>
-      <c r="B1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="n">
+        <v>125756</v>
+      </c>
+      <c r="B1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>235</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>11220</v>
-      </c>
-      <c r="D2">
-        <v>15975</v>
-      </c>
-      <c r="E2">
+      <c r="C2" t="n">
+        <v>14457</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15799</v>
+      </c>
+      <c r="E2" t="n">
         <v>3058</v>
       </c>
-      <c r="F2">
-        <v>5745</v>
-      </c>
-      <c r="G2">
-        <v>8885</v>
-      </c>
-      <c r="H2">
-        <v>12075</v>
-      </c>
-      <c r="I2">
-        <v>6640</v>
-      </c>
-      <c r="J2">
-        <v>4191</v>
+      <c r="F2" t="n">
+        <v>4593</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7954</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12282</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9499</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5124</v>
       </c>
     </row>
   </sheetData>
@@ -746,47 +828,59 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>114667</v>
-      </c>
-      <c r="B1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>12735</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="n">
+        <v>125287</v>
+      </c>
+      <c r="B1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>14931</v>
+      </c>
+      <c r="B2" t="n">
         <v>2031</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>957</v>
       </c>
-      <c r="D2">
-        <v>13958</v>
-      </c>
-      <c r="E2">
-        <v>7771</v>
-      </c>
-      <c r="F2">
+      <c r="D2" t="n">
+        <v>16154</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7562</v>
+      </c>
+      <c r="F2" t="n">
         <v>4623</v>
       </c>
-      <c r="G2">
-        <v>7763</v>
-      </c>
-      <c r="H2">
+      <c r="G2" t="n">
+        <v>11542</v>
+      </c>
+      <c r="H2" t="n">
         <v>1926</v>
       </c>
-      <c r="I2">
-        <v>10148</v>
-      </c>
-      <c r="J2">
+      <c r="I2" t="n">
+        <v>12806</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/code/resultados/NWJSSP_OADG_NEH(SwapMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapMixedImprovement).xlsx
@@ -14,6 +14,8 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m100_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m100_1r" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -424,30 +426,354 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43375936</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1421723</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>63399</v>
+      </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>711357</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>432534</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>98497</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>55144</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>341433</v>
+      </c>
+      <c r="G2" t="n">
+        <v>796116</v>
+      </c>
+      <c r="H2" t="n">
+        <v>661175</v>
+      </c>
+      <c r="I2" t="n">
+        <v>95858</v>
+      </c>
+      <c r="J2" t="n">
+        <v>253696</v>
+      </c>
+      <c r="K2" t="n">
+        <v>811002</v>
+      </c>
+      <c r="L2" t="n">
+        <v>293236</v>
+      </c>
+      <c r="M2" t="n">
+        <v>626258</v>
+      </c>
+      <c r="N2" t="n">
+        <v>625057</v>
+      </c>
+      <c r="O2" t="n">
+        <v>645305</v>
+      </c>
+      <c r="P2" t="n">
+        <v>461161</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>280937</v>
+      </c>
+      <c r="R2" t="n">
+        <v>727147</v>
+      </c>
+      <c r="S2" t="n">
+        <v>576308</v>
+      </c>
+      <c r="T2" t="n">
+        <v>185389</v>
+      </c>
+      <c r="U2" t="n">
+        <v>42097</v>
+      </c>
+      <c r="V2" t="n">
+        <v>812281</v>
+      </c>
+      <c r="W2" t="n">
+        <v>271709</v>
+      </c>
+      <c r="X2" t="n">
+        <v>199537</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>90341</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>479717</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>179804</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>422317</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>799685</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>589699</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>549259</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>323679</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>484561</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>578665</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>150738</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>666460</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>723802</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>368557</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>307171</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>392930</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>421050</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>705</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>332375</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>259148</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>461881</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3102</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>21013</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>468850</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>92765</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>168172</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>532129</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>602824</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>239033</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>381992</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>297349</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>153348</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12994</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>732767</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>185760</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>338661</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>630561</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>776892</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>236636</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>194423</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>66036</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>334937</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>125416</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>106499</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>536398</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>64661</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>438838</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>595876</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>211373</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>697453</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>750447</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>16033</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>131092</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>605565</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>364139</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>118863</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>661350</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>506453</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>22017</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>158981</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>221002</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>60932</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>358462</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>484416</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>530121</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>669608</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>518976</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>207034</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>701342</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>763478</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>678928</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>369036</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>431673</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>393180</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>758205</v>
       </c>
     </row>
   </sheetData>
@@ -466,7 +792,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="B1" t="n">
         <v>1</v>
@@ -474,22 +800,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -508,42 +834,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>12110</v>
+        <v>11416</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>46</v>
+        <v>314</v>
       </c>
       <c r="B2" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>955</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1543</v>
+        <v>1285</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="F2" t="n">
-        <v>1319</v>
+        <v>455</v>
       </c>
       <c r="G2" t="n">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="H2" t="n">
-        <v>377</v>
+        <v>1122</v>
       </c>
       <c r="I2" t="n">
-        <v>1133</v>
+        <v>983</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -562,42 +888,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>12629</v>
+        <v>11699</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="B2" t="n">
-        <v>1441</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1070</v>
+        <v>1360</v>
       </c>
       <c r="E2" t="n">
-        <v>743</v>
+        <v>811</v>
       </c>
       <c r="F2" t="n">
-        <v>1639</v>
+        <v>1022</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1191</v>
       </c>
       <c r="H2" t="n">
-        <v>907</v>
+        <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>768</v>
+        <v>836</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -616,10 +942,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>21767</v>
+        <v>19770</v>
       </c>
       <c r="B1" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -627,46 +953,46 @@
         <v>281</v>
       </c>
       <c r="B2" t="n">
-        <v>496</v>
+        <v>969</v>
       </c>
       <c r="C2" t="n">
-        <v>676</v>
+        <v>606</v>
       </c>
       <c r="D2" t="n">
-        <v>767</v>
+        <v>697</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1603</v>
+        <v>1616</v>
       </c>
       <c r="G2" t="n">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="H2" t="n">
         <v>149</v>
       </c>
       <c r="I2" t="n">
-        <v>1666</v>
+        <v>1639</v>
       </c>
       <c r="J2" t="n">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="K2" t="n">
-        <v>1762</v>
+        <v>916</v>
       </c>
       <c r="L2" t="n">
         <v>180</v>
       </c>
       <c r="M2" t="n">
-        <v>1444</v>
+        <v>1457</v>
       </c>
       <c r="N2" t="n">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="O2" t="n">
-        <v>919</v>
+        <v>849</v>
       </c>
       <c r="P2" t="n">
         <v>399</v>
@@ -675,10 +1001,10 @@
         <v>62</v>
       </c>
       <c r="R2" t="n">
-        <v>1887</v>
+        <v>1116</v>
       </c>
       <c r="S2" t="n">
-        <v>1035</v>
+        <v>437</v>
       </c>
       <c r="T2" t="n">
         <v>348</v>
@@ -700,10 +1026,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>21479</v>
+        <v>19186</v>
       </c>
       <c r="B1" t="n">
-        <v>8</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
@@ -711,58 +1037,58 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1380</v>
+        <v>1269</v>
       </c>
       <c r="C2" t="n">
-        <v>1137</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>1228</v>
+        <v>480</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1951</v>
+        <v>1617</v>
       </c>
       <c r="G2" t="n">
-        <v>1812</v>
+        <v>1162</v>
       </c>
       <c r="H2" t="n">
-        <v>433</v>
+        <v>598</v>
       </c>
       <c r="I2" t="n">
-        <v>1491</v>
+        <v>1380</v>
       </c>
       <c r="J2" t="n">
-        <v>170</v>
+        <v>972</v>
       </c>
       <c r="K2" t="n">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="L2" t="n">
-        <v>531</v>
+        <v>314</v>
       </c>
       <c r="M2" t="n">
-        <v>1643</v>
+        <v>435</v>
       </c>
       <c r="N2" t="n">
-        <v>316</v>
+        <v>1361</v>
       </c>
       <c r="O2" t="n">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="P2" t="n">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="Q2" t="n">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="R2" t="n">
-        <v>880</v>
+        <v>224</v>
       </c>
       <c r="S2" t="n">
-        <v>101</v>
+        <v>836</v>
       </c>
       <c r="T2" t="n">
         <v>74</v>
@@ -784,42 +1110,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>125756</v>
+        <v>114054</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>235</v>
+        <v>9450</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>14457</v>
+        <v>12366</v>
       </c>
       <c r="D2" t="n">
-        <v>15799</v>
+        <v>898</v>
       </c>
       <c r="E2" t="n">
-        <v>3058</v>
+        <v>7591</v>
       </c>
       <c r="F2" t="n">
-        <v>4593</v>
+        <v>2592</v>
       </c>
       <c r="G2" t="n">
-        <v>7954</v>
+        <v>2446</v>
       </c>
       <c r="H2" t="n">
-        <v>12282</v>
+        <v>12794</v>
       </c>
       <c r="I2" t="n">
-        <v>9499</v>
+        <v>10011</v>
       </c>
       <c r="J2" t="n">
-        <v>5124</v>
+        <v>3151</v>
       </c>
     </row>
   </sheetData>
@@ -838,10 +1164,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>125287</v>
+        <v>105446</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -854,16 +1180,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14931</v>
+        <v>712</v>
       </c>
       <c r="B2" t="n">
         <v>2031</v>
       </c>
       <c r="C2" t="n">
-        <v>957</v>
+        <v>848</v>
       </c>
       <c r="D2" t="n">
-        <v>16154</v>
+        <v>9593</v>
       </c>
       <c r="E2" t="n">
         <v>7562</v>
@@ -872,16 +1198,340 @@
         <v>4623</v>
       </c>
       <c r="G2" t="n">
-        <v>11542</v>
+        <v>4661</v>
       </c>
       <c r="H2" t="n">
-        <v>1926</v>
+        <v>12722</v>
       </c>
       <c r="I2" t="n">
-        <v>12806</v>
+        <v>9939</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43803478</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1986515</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>104334</v>
+      </c>
+      <c r="B2" t="n">
+        <v>181722</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>741395</v>
+      </c>
+      <c r="E2" t="n">
+        <v>701773</v>
+      </c>
+      <c r="F2" t="n">
+        <v>648009</v>
+      </c>
+      <c r="G2" t="n">
+        <v>591235</v>
+      </c>
+      <c r="H2" t="n">
+        <v>812905</v>
+      </c>
+      <c r="I2" t="n">
+        <v>300584</v>
+      </c>
+      <c r="J2" t="n">
+        <v>140782</v>
+      </c>
+      <c r="K2" t="n">
+        <v>709416</v>
+      </c>
+      <c r="L2" t="n">
+        <v>602961</v>
+      </c>
+      <c r="M2" t="n">
+        <v>508053</v>
+      </c>
+      <c r="N2" t="n">
+        <v>458602</v>
+      </c>
+      <c r="O2" t="n">
+        <v>309349</v>
+      </c>
+      <c r="P2" t="n">
+        <v>40870</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>394003</v>
+      </c>
+      <c r="R2" t="n">
+        <v>174092</v>
+      </c>
+      <c r="S2" t="n">
+        <v>119057</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230215</v>
+      </c>
+      <c r="U2" t="n">
+        <v>339422</v>
+      </c>
+      <c r="V2" t="n">
+        <v>629066</v>
+      </c>
+      <c r="W2" t="n">
+        <v>482771</v>
+      </c>
+      <c r="X2" t="n">
+        <v>416261</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>74929</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>212179</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>786624</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>138830</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>571292</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>35886</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>449870</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>519891</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>238236</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>359299</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>258350</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>667270</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>316679</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>597025</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>374096</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>383529</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>735045</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>57065</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>616402</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>254298</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9091</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>88599</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>426364</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>49356</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>30854</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>362303</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>379887</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>719756</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>333572</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>445702</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>218033</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>775204</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>695450</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>326563</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>36777</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>545376</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>541390</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>426</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>180612</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>285213</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>504845</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>138773</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>443273</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>791460</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>306675</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>154097</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>270027</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>259667</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>644179</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>161998</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>685805</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>488977</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>361251</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>802006</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>731604</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>65017</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>667660</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>94744</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>124196</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>207337</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>762168</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>572349</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>17702</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>643836</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>322400</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>537955</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>455527</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>262536</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>110744</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>419875</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>396823</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>596016</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>759185</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>760546</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>548232</v>
       </c>
     </row>
   </sheetData>
